--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/SOUTH_CAROLINA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/SOUTH_CAROLINA_2018.xlsx
@@ -499,7 +499,7 @@
         <v>8</v>
       </c>
       <c r="D8">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="9">
@@ -823,7 +823,7 @@
         <v>8</v>
       </c>
       <c r="D26">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="27">
@@ -841,7 +841,7 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="28">
@@ -877,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="D29">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="30">
@@ -1759,7 +1759,7 @@
         <v>8</v>
       </c>
       <c r="D78">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="79">
@@ -3613,7 +3613,7 @@
         <v>8</v>
       </c>
       <c r="D181">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="182">
@@ -4099,7 +4099,7 @@
         <v>8</v>
       </c>
       <c r="D208">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="209">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C225">
@@ -6799,7 +6799,7 @@
         <v>8</v>
       </c>
       <c r="D358">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="359">
@@ -6961,7 +6961,7 @@
         <v>8</v>
       </c>
       <c r="D367">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="368">
@@ -10147,7 +10147,7 @@
         <v>8</v>
       </c>
       <c r="D544">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="545">
@@ -10597,7 +10597,7 @@
         <v>8</v>
       </c>
       <c r="D569">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="570">
@@ -10777,7 +10777,7 @@
         <v>8</v>
       </c>
       <c r="D579">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="580">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C624">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C665">
@@ -12631,7 +12631,7 @@
         <v>8</v>
       </c>
       <c r="D682">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="683">
@@ -13405,7 +13405,7 @@
         <v>8</v>
       </c>
       <c r="D725">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="726">
@@ -14773,7 +14773,7 @@
         <v>8</v>
       </c>
       <c r="D801">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="802">
@@ -15727,7 +15727,7 @@
         <v>8</v>
       </c>
       <c r="D854">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="855">
@@ -16159,7 +16159,7 @@
         <v>8</v>
       </c>
       <c r="D878">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="879">
@@ -16483,7 +16483,7 @@
         <v>8</v>
       </c>
       <c r="D896">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="897">
@@ -19273,7 +19273,7 @@
         <v>8</v>
       </c>
       <c r="D1051">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="1052">
@@ -19525,7 +19525,7 @@
         <v>8</v>
       </c>
       <c r="D1065">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="1066">
@@ -19885,7 +19885,7 @@
         <v>8</v>
       </c>
       <c r="D1085">
-        <v>0.0009941593140300733</v>
+        <v>0.0009941593140300731</v>
       </c>
     </row>
     <row r="1086">
